--- a/BD.xlsx
+++ b/BD.xlsx
@@ -119,7 +119,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="105">
   <si>
     <t>Имя файла</t>
   </si>
@@ -413,6 +413,27 @@
   </si>
   <si>
     <t>0.0006</t>
+  </si>
+  <si>
+    <t>≈ (2.41)</t>
+  </si>
+  <si>
+    <t>≈ (10)</t>
+  </si>
+  <si>
+    <t>≈ (1.03)</t>
+  </si>
+  <si>
+    <t>≈ (4.67)</t>
+  </si>
+  <si>
+    <t>≈ (6.3)</t>
+  </si>
+  <si>
+    <t>≈ (1)</t>
+  </si>
+  <si>
+    <t>0.14</t>
   </si>
 </sst>
 </file>
@@ -426,7 +447,7 @@
     <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="mmm\.yy"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,6 +563,21 @@
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1054,137 +1090,137 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1315,6 +1351,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
@@ -2657,7 +2705,7 @@
       <c r="C20" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="48" t="s">
         <v>86</v>
       </c>
       <c r="G20" s="12" t="s">
@@ -2692,7 +2740,7 @@
       <c r="E21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="44" t="s">
+      <c r="F21" s="48" t="s">
         <v>89</v>
       </c>
       <c r="G21" s="12" t="s">
@@ -2817,11 +2865,126 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" ht="46" customHeight="1"/>
-    <row r="26" ht="46" customHeight="1"/>
-    <row r="27" ht="46" customHeight="1"/>
-    <row r="28" ht="46" customHeight="1"/>
-    <row r="29" ht="46" customHeight="1"/>
+    <row r="25" ht="46" customHeight="1" spans="1:17">
+      <c r="A25" s="44">
+        <v>24</v>
+      </c>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="I25" s="46" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" ht="46" customHeight="1" spans="1:17">
+      <c r="A26" s="47">
+        <v>25</v>
+      </c>
+      <c r="G26" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" ht="46" customHeight="1" spans="1:17">
+      <c r="A27" s="47">
+        <v>26</v>
+      </c>
+      <c r="G27" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" ht="46" customHeight="1" spans="1:17">
+      <c r="A28" s="47">
+        <v>27</v>
+      </c>
+      <c r="G28" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" ht="46" customHeight="1" spans="1:17">
+      <c r="A29" s="47">
+        <v>28</v>
+      </c>
+      <c r="G29" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
     <row r="30" ht="46" customHeight="1"/>
     <row r="31" ht="46" customHeight="1"/>
     <row r="32" ht="46" customHeight="1"/>

--- a/BD.xlsx
+++ b/BD.xlsx
@@ -1353,9 +1353,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1363,6 +1360,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1">
@@ -2866,21 +2866,21 @@
       </c>
     </row>
     <row r="25" ht="46" customHeight="1" spans="1:17">
-      <c r="A25" s="44">
+      <c r="A25" s="40">
         <v>24</v>
       </c>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="45" t="s">
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="H25" s="46" t="s">
+      <c r="H25" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="I25" s="46" t="s">
+      <c r="I25" s="45" t="s">
         <v>35</v>
       </c>
       <c r="J25" s="9" t="s">
@@ -2894,10 +2894,10 @@
       </c>
     </row>
     <row r="26" ht="46" customHeight="1" spans="1:17">
-      <c r="A26" s="47">
+      <c r="A26" s="46">
         <v>25</v>
       </c>
-      <c r="G26" s="45" t="s">
+      <c r="G26" s="44" t="s">
         <v>95</v>
       </c>
       <c r="H26" s="6" t="s">
@@ -2917,10 +2917,10 @@
       </c>
     </row>
     <row r="27" ht="46" customHeight="1" spans="1:17">
-      <c r="A27" s="47">
+      <c r="A27" s="46">
         <v>26</v>
       </c>
-      <c r="G27" s="45" t="s">
+      <c r="G27" s="44" t="s">
         <v>95</v>
       </c>
       <c r="H27" s="6" t="s">
@@ -2940,10 +2940,10 @@
       </c>
     </row>
     <row r="28" ht="46" customHeight="1" spans="1:17">
-      <c r="A28" s="47">
+      <c r="A28" s="46">
         <v>27</v>
       </c>
-      <c r="G28" s="45" t="s">
+      <c r="G28" s="44" t="s">
         <v>95</v>
       </c>
       <c r="H28" s="6" t="s">
@@ -2966,7 +2966,7 @@
       <c r="A29" s="47">
         <v>28</v>
       </c>
-      <c r="G29" s="45" t="s">
+      <c r="G29" s="44" t="s">
         <v>95</v>
       </c>
       <c r="H29" s="6" t="s">
